--- a/plantillas-carga/Plantillas_Master.xlsx
+++ b/plantillas-carga/Plantillas_Master.xlsx
@@ -2850,7 +2850,7 @@
     <row r="46">
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>· destinos (vieja) — Ya no se usa: orígenes y destinos viven en `lugares`. La tabla vieja queda solo por compatibilidad.</t>
+          <t>· destinos (vieja) — Ya no se usa: el origen y el destino se escriben en cada ruta. La tabla vieja queda solo por compatibilidad.</t>
         </is>
       </c>
     </row>
